--- a/data/templates/cold_storage_status_template.xlsx
+++ b/data/templates/cold_storage_status_template.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,15 +424,45 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>cold_storage_total_capacity_qty</t>
+          <t>total_capacity_qty</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>cold_storage_current_qty</t>
+          <t>current_occupied_qty</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
+        <is>
+          <t>expected_inbound_qty</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>expected_outbound_qty</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>warning_threshold_qty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>projected_occupied_qty</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>remaining_capacity_qty</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
